--- a/webapp/public/templates/3. BÁO CÁO MYTV_TÂN.xlsx
+++ b/webapp/public/templates/3. BÁO CÁO MYTV_TÂN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\quyng\Documents\TOOL TỔNG HỢP BÁO CÁO\BÁO CÁO TUẦN 29\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\quyng\Documents\TOOL TỔNG HỢP BÁO CÁO\VNPT REPORT\data sample\DATA SAMPLE THANG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00585BDC-E848-43DC-9454-44A45B178E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC908C6C-17AA-4754-89C4-87B3CB517C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>STT</t>
   </si>
@@ -148,12 +148,15 @@
   <si>
     <t>Column8</t>
   </si>
+  <si>
+    <t>B12_TAN</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -308,6 +311,12 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -987,60 +996,6 @@
   <dxfs count="12">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="0"/>
-        <name val="Calibri Light"/>
-        <family val="1"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1362,6 +1317,60 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="0"/>
+        <name val="Calibri Light"/>
+        <family val="1"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1376,17 +1385,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F8584BF8-CAD7-4616-ADFD-20EDBD4739CB}" name="b1_tan" displayName="b1_tan" ref="A1:H16" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="10" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F8584BF8-CAD7-4616-ADFD-20EDBD4739CB}" name="b1_tan" displayName="b1_tan" ref="A1:H16" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9">
   <autoFilter ref="A1:H16" xr:uid="{F8584BF8-CAD7-4616-ADFD-20EDBD4739CB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{836BF3E7-8462-4889-AC6C-7F372FEE7094}" name="Column1" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{29B640B9-ADE9-4F62-BBE7-3584C8B5DBA2}" name="Column2" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{BB5ED37F-5C9D-4A89-A8D0-EFF86CF04754}" name="Column3" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{F0994BD3-692F-4AFA-BDFA-D89F81D9040D}" name="Column4" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{8715FA61-4B54-493A-8EA8-DFBD08D8557F}" name="Column5" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{21DE4923-AB9C-47D7-A893-B0C7F39FC0E0}" name="Column6" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{CD347CF4-083C-4A7E-B945-68363A5DA853}" name="Column7" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{EEB7B45E-D02A-4111-8D6B-FD41B4E516F9}" name="Column8" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{836BF3E7-8462-4889-AC6C-7F372FEE7094}" name="Column1" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{29B640B9-ADE9-4F62-BBE7-3584C8B5DBA2}" name="Column2" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{BB5ED37F-5C9D-4A89-A8D0-EFF86CF04754}" name="Column3" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{F0994BD3-692F-4AFA-BDFA-D89F81D9040D}" name="Column4" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{8715FA61-4B54-493A-8EA8-DFBD08D8557F}" name="Column5" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{21DE4923-AB9C-47D7-A893-B0C7F39FC0E0}" name="Column6" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{CD347CF4-083C-4A7E-B945-68363A5DA853}" name="Column7" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{EEB7B45E-D02A-4111-8D6B-FD41B4E516F9}" name="Column8" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1655,7 +1664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB4DFF3-F3BA-4A24-9C19-803BFB0B8F37}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -1666,7 +1675,7 @@
     <col min="7" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>28</v>
       </c>
@@ -1692,7 +1701,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -1715,8 +1724,11 @@
       <c r="H2" s="16" t="s">
         <v>24</v>
       </c>
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>1</v>
       </c>
@@ -1742,7 +1754,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="9"/>
       <c r="C4" s="2"/>
@@ -1756,7 +1768,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="17"/>
     </row>
-    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="13"/>
       <c r="B5" s="9"/>
       <c r="C5" s="2"/>
@@ -1770,7 +1782,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="17"/>
     </row>
-    <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14"/>
       <c r="B6" s="10"/>
       <c r="C6" s="4"/>
@@ -1784,7 +1796,7 @@
       <c r="G6" s="4"/>
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:8" ht="300" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="300" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
         <v>2</v>
       </c>
@@ -1810,7 +1822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="9"/>
       <c r="C8" s="2"/>
@@ -1824,7 +1836,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="17"/>
     </row>
-    <row r="9" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="9"/>
       <c r="C9" s="2"/>
@@ -1838,7 +1850,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="17"/>
     </row>
-    <row r="10" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="9"/>
       <c r="C10" s="2"/>
@@ -1852,7 +1864,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="17"/>
     </row>
-    <row r="11" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="9"/>
       <c r="C11" s="2"/>
@@ -1866,7 +1878,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="17"/>
     </row>
-    <row r="12" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="9"/>
       <c r="C12" s="2"/>
@@ -1880,7 +1892,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="17"/>
     </row>
-    <row r="13" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="9"/>
       <c r="C13" s="2"/>
@@ -1894,7 +1906,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="17"/>
     </row>
-    <row r="14" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="9"/>
       <c r="C14" s="2"/>
@@ -1908,7 +1920,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="17"/>
     </row>
-    <row r="15" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="9"/>
       <c r="C15" s="2"/>
@@ -1922,7 +1934,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="17"/>
     </row>
-    <row r="16" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A16" s="23"/>
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
@@ -1937,6 +1949,7 @@
       <c r="H16" s="27"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
